--- a/Learning DSA Resources/Practice DSA/DSA by Shradha Didi & Aman Bhaiya.xlsx
+++ b/Learning DSA Resources/Practice DSA/DSA by Shradha Didi & Aman Bhaiya.xlsx
@@ -7,17 +7,17 @@
     <sheet state="visible" name="Bonus DSA Questions" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="Z_789ACEED_B5B0_4AFC_A629_C77930C929B0_.wvu.FilterData">'DSA in 2.5 Months'!$A$11:$C$37</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_67345B07_30D1_4E06_A949_5CFECF7BCDC2_.wvu.FilterData">'DSA in 2.5 Months'!$A$293:$C$332</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_CAAD60BF_9A00_4E7A_920F_5B887B529C05_.wvu.FilterData">'DSA in 2.5 Months'!$A$11:$D$37</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_08CEC5F7_8997_49F5_A5AA_0E8152627A36_.wvu.FilterData">'DSA in 2.5 Months'!$A$11:$D$37</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_50A8DEAE_F3A0_4955_AB2E_054375A5BA07_.wvu.FilterData">'DSA in 2.5 Months'!$A$293:$C$332</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_01BE6A79_C28F_4EC2_918B_245CDF1C8B15_.wvu.FilterData">'DSA in 2.5 Months'!$A$11:$C$37</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_ED3A6955_A34E_4ADD_BF3B_C5EDCC341184_.wvu.FilterData">'DSA in 2.5 Months'!$A$11:$D$37</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_C5C525AF_A44C_4AB2_BEA9_61D43760BDB4_.wvu.FilterData">'DSA in 2.5 Months'!$A$11:$D$37</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{CAAD60BF-9A00-4E7A-920F-5B887B529C05}" name="Filter 4"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{789ACEED-B5B0-4AFC-A629-C77930C929B0}" name="Filter 2"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{08CEC5F7-8997-49F5-A5AA-0E8152627A36}" name="Filter 3"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{67345B07-30D1-4E06-A949-5CFECF7BCDC2}" name="Filter 1"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{ED3A6955-A34E-4ADD-BF3B-C5EDCC341184}" name="Filter 4"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{01BE6A79-C28F-4EC2-918B-245CDF1C8B15}" name="Filter 2"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{C5C525AF-A44C-4AB2-BEA9-61D43760BDB4}" name="Filter 3"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{50A8DEAE-F3A0-4955-AB2E-054375A5BA07}" name="Filter 1"/>
   </customWorkbookViews>
 </workbook>
 </file>
@@ -21239,16 +21239,16 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{CAAD60BF-9A00-4E7A-920F-5B887B529C05}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{ED3A6955-A34E-4ADD-BF3B-C5EDCC341184}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$11:$D$37"/>
     </customSheetView>
-    <customSheetView guid="{67345B07-30D1-4E06-A949-5CFECF7BCDC2}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{50A8DEAE-F3A0-4955-AB2E-054375A5BA07}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$293:$C$332"/>
     </customSheetView>
-    <customSheetView guid="{789ACEED-B5B0-4AFC-A629-C77930C929B0}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{01BE6A79-C28F-4EC2-918B-245CDF1C8B15}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$11:$C$37"/>
     </customSheetView>
-    <customSheetView guid="{08CEC5F7-8997-49F5-A5AA-0E8152627A36}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{C5C525AF-A44C-4AB2-BEA9-61D43760BDB4}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$11:$D$37"/>
     </customSheetView>
   </customSheetViews>
